--- a/research/traditional_assets/database/data/switzerland/switzerland_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_computers_peripherals.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.227</v>
+        <v>0.172</v>
       </c>
       <c r="E2">
-        <v>0.418</v>
+        <v>0.168</v>
       </c>
       <c r="F2">
-        <v>-0.0256</v>
+        <v>0.0301</v>
       </c>
       <c r="G2">
-        <v>0.2572316888827814</v>
+        <v>0.2324425709644984</v>
       </c>
       <c r="H2">
-        <v>0.2117802665933764</v>
+        <v>0.1747234898290664</v>
       </c>
       <c r="I2">
-        <v>0.1942039892118368</v>
+        <v>0.128690461739143</v>
       </c>
       <c r="J2">
-        <v>0.1615370668542032</v>
+        <v>0.1041829420508132</v>
       </c>
       <c r="K2">
-        <v>934.6</v>
+        <v>501.1</v>
       </c>
       <c r="L2">
-        <v>0.1605400577160918</v>
+        <v>0.09689457808028464</v>
       </c>
       <c r="M2">
-        <v>537.4</v>
+        <v>670.0999999999999</v>
       </c>
       <c r="N2">
-        <v>0.03815568998324387</v>
+        <v>0.06717390432655679</v>
       </c>
       <c r="O2">
-        <v>0.5750053498823026</v>
+        <v>1.337258032328876</v>
       </c>
       <c r="P2">
-        <v>159.4</v>
+        <v>158.7</v>
       </c>
       <c r="Q2">
-        <v>0.0113174860128937</v>
+        <v>0.01590881751473595</v>
       </c>
       <c r="R2">
-        <v>0.1705542478065483</v>
+        <v>0.3167032528437437</v>
       </c>
       <c r="S2">
-        <v>378</v>
+        <v>511.3999999999999</v>
       </c>
       <c r="T2">
-        <v>0.7033866765909937</v>
+        <v>0.7631696761677361</v>
       </c>
       <c r="U2">
-        <v>1137.3</v>
+        <v>868.5</v>
       </c>
       <c r="V2">
-        <v>0.08074891369174406</v>
+        <v>0.08706243233489715</v>
       </c>
       <c r="W2">
-        <v>0.547831184056272</v>
+        <v>0.2214610863128122</v>
       </c>
       <c r="X2">
-        <v>0.06830887916863326</v>
+        <v>0.1112916970403925</v>
       </c>
       <c r="Y2">
-        <v>0.4795223048876387</v>
+        <v>0.1101693892724196</v>
       </c>
       <c r="Z2">
-        <v>13.79819418503407</v>
+        <v>7.239871805539615</v>
       </c>
       <c r="AA2">
-        <v>2.228919816535126</v>
+        <v>0.7542711447718502</v>
       </c>
       <c r="AB2">
-        <v>0.06819182810975093</v>
+        <v>0.111038389607546</v>
       </c>
       <c r="AC2">
-        <v>2.160727988425375</v>
+        <v>0.6432327551643042</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>34.11028202185186</v>
+        <v>38.32204034924094</v>
       </c>
       <c r="AF2">
-        <v>34.11028202185186</v>
+        <v>38.32204034924094</v>
       </c>
       <c r="AG2">
-        <v>-1103.189717978148</v>
+        <v>-830.177959650759</v>
       </c>
       <c r="AH2">
-        <v>0.002415997250452622</v>
+        <v>0.0038268762423783</v>
       </c>
       <c r="AI2">
-        <v>0.01485115348396343</v>
+        <v>0.01736447398168019</v>
       </c>
       <c r="AJ2">
-        <v>-0.08498357965173675</v>
+        <v>-0.09077524864222193</v>
       </c>
       <c r="AK2">
-        <v>-0.9514272836412483</v>
+        <v>-0.6202662049962482</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.17</v>
+        <v>-5.64</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.8901716436521812</v>
+        <v>-1.063921516917543</v>
       </c>
       <c r="AQ2">
-        <v>-960.3418803418804</v>
+        <v>-116.790780141844</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.227</v>
+        <v>0.172</v>
       </c>
       <c r="E3">
-        <v>0.418</v>
+        <v>0.168</v>
       </c>
       <c r="F3">
-        <v>-0.0256</v>
+        <v>0.0301</v>
       </c>
       <c r="G3">
-        <v>0.2572316888827814</v>
+        <v>0.2324425709644984</v>
       </c>
       <c r="H3">
-        <v>0.2117802665933764</v>
+        <v>0.1747234898290664</v>
       </c>
       <c r="I3">
-        <v>0.1942039892118368</v>
+        <v>0.128690461739143</v>
       </c>
       <c r="J3">
-        <v>0.1615370668542032</v>
+        <v>0.1041829420508132</v>
       </c>
       <c r="K3">
-        <v>934.6</v>
+        <v>501.1</v>
       </c>
       <c r="L3">
-        <v>0.1605400577160918</v>
+        <v>0.09689457808028464</v>
       </c>
       <c r="M3">
-        <v>537.4</v>
+        <v>670.0999999999999</v>
       </c>
       <c r="N3">
-        <v>0.03815568998324387</v>
+        <v>0.06717390432655679</v>
       </c>
       <c r="O3">
-        <v>0.5750053498823026</v>
+        <v>1.337258032328876</v>
       </c>
       <c r="P3">
-        <v>159.4</v>
+        <v>158.7</v>
       </c>
       <c r="Q3">
-        <v>0.0113174860128937</v>
+        <v>0.01590881751473595</v>
       </c>
       <c r="R3">
-        <v>0.1705542478065483</v>
+        <v>0.3167032528437437</v>
       </c>
       <c r="S3">
-        <v>378</v>
+        <v>511.3999999999999</v>
       </c>
       <c r="T3">
-        <v>0.7033866765909937</v>
+        <v>0.7631696761677361</v>
       </c>
       <c r="U3">
-        <v>1137.3</v>
+        <v>868.5</v>
       </c>
       <c r="V3">
-        <v>0.08074891369174406</v>
+        <v>0.08706243233489715</v>
       </c>
       <c r="W3">
-        <v>0.547831184056272</v>
+        <v>0.2214610863128122</v>
       </c>
       <c r="X3">
-        <v>0.06830887916863326</v>
+        <v>0.1112916970403925</v>
       </c>
       <c r="Y3">
-        <v>0.4795223048876387</v>
+        <v>0.1101693892724196</v>
       </c>
       <c r="Z3">
-        <v>13.79819418503407</v>
+        <v>7.239871805539615</v>
       </c>
       <c r="AA3">
-        <v>2.228919816535126</v>
+        <v>0.7542711447718502</v>
       </c>
       <c r="AB3">
-        <v>0.06819182810975093</v>
+        <v>0.111038389607546</v>
       </c>
       <c r="AC3">
-        <v>2.160727988425375</v>
+        <v>0.6432327551643042</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>34.11028202185186</v>
+        <v>38.32204034924094</v>
       </c>
       <c r="AF3">
-        <v>34.11028202185186</v>
+        <v>38.32204034924094</v>
       </c>
       <c r="AG3">
-        <v>-1103.189717978148</v>
+        <v>-830.177959650759</v>
       </c>
       <c r="AH3">
-        <v>0.002415997250452622</v>
+        <v>0.0038268762423783</v>
       </c>
       <c r="AI3">
-        <v>0.01485115348396343</v>
+        <v>0.01736447398168019</v>
       </c>
       <c r="AJ3">
-        <v>-0.08498357965173675</v>
+        <v>-0.09077524864222193</v>
       </c>
       <c r="AK3">
-        <v>-0.9514272836412483</v>
+        <v>-0.6202662049962482</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.17</v>
+        <v>-5.64</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.8901716436521812</v>
+        <v>-1.063921516917543</v>
       </c>
       <c r="AQ3">
-        <v>-960.3418803418804</v>
+        <v>-116.790780141844</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_computers_peripherals.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.172</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="E2">
-        <v>0.168</v>
+        <v>0.119</v>
       </c>
       <c r="F2">
-        <v>0.0301</v>
+        <v>0.123</v>
       </c>
       <c r="G2">
-        <v>0.2324425709644984</v>
+        <v>0.2052328992138918</v>
       </c>
       <c r="H2">
-        <v>0.1747234898290664</v>
+        <v>0.1406077672181157</v>
       </c>
       <c r="I2">
-        <v>0.128690461739143</v>
+        <v>0.1126537020290641</v>
       </c>
       <c r="J2">
-        <v>0.1041829420508132</v>
+        <v>0.08987324827287317</v>
       </c>
       <c r="K2">
-        <v>501.1</v>
+        <v>381.5</v>
       </c>
       <c r="L2">
-        <v>0.09689457808028464</v>
+        <v>0.08952246861433767</v>
       </c>
       <c r="M2">
-        <v>670.0999999999999</v>
+        <v>580.7</v>
       </c>
       <c r="N2">
-        <v>0.06717390432655679</v>
+        <v>0.03910306050301337</v>
       </c>
       <c r="O2">
-        <v>1.337258032328876</v>
+        <v>1.522149410222805</v>
       </c>
       <c r="P2">
-        <v>158.7</v>
+        <v>182.3</v>
       </c>
       <c r="Q2">
-        <v>0.01590881751473595</v>
+        <v>0.01227568095350325</v>
       </c>
       <c r="R2">
-        <v>0.3167032528437437</v>
+        <v>0.4778505897771953</v>
       </c>
       <c r="S2">
-        <v>511.3999999999999</v>
+        <v>398.4</v>
       </c>
       <c r="T2">
-        <v>0.7631696761677361</v>
+        <v>0.6860685379714138</v>
       </c>
       <c r="U2">
-        <v>868.5</v>
+        <v>1163.9</v>
       </c>
       <c r="V2">
-        <v>0.08706243233489715</v>
+        <v>0.07837446550621192</v>
       </c>
       <c r="W2">
-        <v>0.2214610863128122</v>
+        <v>0.1759199483537766</v>
       </c>
       <c r="X2">
-        <v>0.1112916970403925</v>
+        <v>0.09641527864192595</v>
       </c>
       <c r="Y2">
-        <v>0.1101693892724196</v>
+        <v>0.07950466971185069</v>
       </c>
       <c r="Z2">
-        <v>7.239871805539615</v>
+        <v>4.590495071097544</v>
       </c>
       <c r="AA2">
-        <v>0.7542711447718502</v>
+        <v>0.4125627032201502</v>
       </c>
       <c r="AB2">
-        <v>0.111038389607546</v>
+        <v>0.09613797308156782</v>
       </c>
       <c r="AC2">
-        <v>0.6432327551643042</v>
+        <v>0.3164247301385823</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>38.32204034924094</v>
+        <v>78.13124401571699</v>
       </c>
       <c r="AF2">
-        <v>38.32204034924094</v>
+        <v>78.13124401571699</v>
       </c>
       <c r="AG2">
-        <v>-830.177959650759</v>
+        <v>-1085.768755984283</v>
       </c>
       <c r="AH2">
-        <v>0.0038268762423783</v>
+        <v>0.005233650877875133</v>
       </c>
       <c r="AI2">
-        <v>0.01736447398168019</v>
+        <v>0.03624854387382503</v>
       </c>
       <c r="AJ2">
-        <v>-0.09077524864222193</v>
+        <v>-0.07888049078011068</v>
       </c>
       <c r="AK2">
-        <v>-0.6202662049962482</v>
+        <v>-1.095042402886774</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-5.64</v>
+        <v>-35.1</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.063921516917543</v>
+        <v>-1.832211873075064</v>
       </c>
       <c r="AQ2">
-        <v>-116.790780141844</v>
+        <v>-13.74074074074074</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.172</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="E3">
-        <v>0.168</v>
+        <v>0.119</v>
       </c>
       <c r="F3">
-        <v>0.0301</v>
+        <v>0.123</v>
       </c>
       <c r="G3">
-        <v>0.2324425709644984</v>
+        <v>0.2052328992138918</v>
       </c>
       <c r="H3">
-        <v>0.1747234898290664</v>
+        <v>0.1406077672181157</v>
       </c>
       <c r="I3">
-        <v>0.128690461739143</v>
+        <v>0.1126537020290641</v>
       </c>
       <c r="J3">
-        <v>0.1041829420508132</v>
+        <v>0.08987324827287317</v>
       </c>
       <c r="K3">
-        <v>501.1</v>
+        <v>381.5</v>
       </c>
       <c r="L3">
-        <v>0.09689457808028464</v>
+        <v>0.08952246861433767</v>
       </c>
       <c r="M3">
-        <v>670.0999999999999</v>
+        <v>580.7</v>
       </c>
       <c r="N3">
-        <v>0.06717390432655679</v>
+        <v>0.03910306050301337</v>
       </c>
       <c r="O3">
-        <v>1.337258032328876</v>
+        <v>1.522149410222805</v>
       </c>
       <c r="P3">
-        <v>158.7</v>
+        <v>182.3</v>
       </c>
       <c r="Q3">
-        <v>0.01590881751473595</v>
+        <v>0.01227568095350325</v>
       </c>
       <c r="R3">
-        <v>0.3167032528437437</v>
+        <v>0.4778505897771953</v>
       </c>
       <c r="S3">
-        <v>511.3999999999999</v>
+        <v>398.4</v>
       </c>
       <c r="T3">
-        <v>0.7631696761677361</v>
+        <v>0.6860685379714138</v>
       </c>
       <c r="U3">
-        <v>868.5</v>
+        <v>1163.9</v>
       </c>
       <c r="V3">
-        <v>0.08706243233489715</v>
+        <v>0.07837446550621192</v>
       </c>
       <c r="W3">
-        <v>0.2214610863128122</v>
+        <v>0.1759199483537766</v>
       </c>
       <c r="X3">
-        <v>0.1112916970403925</v>
+        <v>0.09641527864192595</v>
       </c>
       <c r="Y3">
-        <v>0.1101693892724196</v>
+        <v>0.07950466971185069</v>
       </c>
       <c r="Z3">
-        <v>7.239871805539615</v>
+        <v>4.590495071097544</v>
       </c>
       <c r="AA3">
-        <v>0.7542711447718502</v>
+        <v>0.4125627032201502</v>
       </c>
       <c r="AB3">
-        <v>0.111038389607546</v>
+        <v>0.09613797308156782</v>
       </c>
       <c r="AC3">
-        <v>0.6432327551643042</v>
+        <v>0.3164247301385823</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>38.32204034924094</v>
+        <v>78.13124401571699</v>
       </c>
       <c r="AF3">
-        <v>38.32204034924094</v>
+        <v>78.13124401571699</v>
       </c>
       <c r="AG3">
-        <v>-830.177959650759</v>
+        <v>-1085.768755984283</v>
       </c>
       <c r="AH3">
-        <v>0.0038268762423783</v>
+        <v>0.005233650877875133</v>
       </c>
       <c r="AI3">
-        <v>0.01736447398168019</v>
+        <v>0.03624854387382503</v>
       </c>
       <c r="AJ3">
-        <v>-0.09077524864222193</v>
+        <v>-0.07888049078011068</v>
       </c>
       <c r="AK3">
-        <v>-0.6202662049962482</v>
+        <v>-1.095042402886774</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-5.64</v>
+        <v>-35.1</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.063921516917543</v>
+        <v>-1.832211873075064</v>
       </c>
       <c r="AQ3">
-        <v>-116.790780141844</v>
+        <v>-13.74074074074074</v>
       </c>
     </row>
   </sheetData>
